--- a/data/trans_bre/P45C_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,18</t>
+          <t>-4,55; -0,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,76</t>
+          <t>-4,08; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,22</t>
+          <t>-2,93; 2,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; -2,46</t>
+          <t>-9,23; -2,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -2,65</t>
+          <t>-43,07; -1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,3; 8,28</t>
+          <t>-33,12; 8,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 42,44</t>
+          <t>-34,71; 38,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -20,21</t>
+          <t>-53,35; -17,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,05</t>
+          <t>-6,37; -1,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,1</t>
+          <t>-6,13; -1,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,78</t>
+          <t>-1,92; 2,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,9</t>
+          <t>-6,94; 2,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,17; -5,27</t>
+          <t>-31,84; -6,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,97; -6,04</t>
+          <t>-29,03; -5,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 19,81</t>
+          <t>-11,34; 19,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 11,36</t>
+          <t>-39,34; 12,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,3</t>
+          <t>-4,45; 5,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -1,85</t>
+          <t>-12,33; -1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,0</t>
+          <t>-2,69; 7,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 3,83</t>
+          <t>-3,98; 3,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 32,86</t>
+          <t>-21,68; 36,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,45; -9,13</t>
+          <t>-49,54; -8,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 52,27</t>
+          <t>-15,42; 52,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 32,02</t>
+          <t>-24,77; 30,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,54</t>
+          <t>-5,02; -1,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -2,55</t>
+          <t>-6,18; -2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,73</t>
+          <t>-1,56; 1,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,52</t>
+          <t>-5,77; 0,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -10,23</t>
+          <t>-30,18; -11,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,79; -14,92</t>
+          <t>-33,38; -14,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 13,72</t>
+          <t>-11,04; 13,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 1,3</t>
+          <t>-34,53; 0,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>-5,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-38,83%</t>
+          <t>-36,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,22</t>
+          <t>-4,6; -0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,86</t>
+          <t>-4,67; 0,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,0</t>
+          <t>-2,78; 2,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -2,24</t>
+          <t>-8,83; -1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,07; -1,9</t>
+          <t>-43,52; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 8,92</t>
+          <t>-34,32; 7,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 38,68</t>
+          <t>-34,07; 39,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -17,54</t>
+          <t>-51,58; -15,32</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,71%</t>
+          <t>-19,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,22</t>
+          <t>-6,27; -1,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -1,11</t>
+          <t>-6,13; -1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,81</t>
+          <t>-1,74; 2,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,34</t>
+          <t>-6,02; -0,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,84; -6,94</t>
+          <t>-30,73; -5,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,03; -5,98</t>
+          <t>-29,19; -5,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 19,83</t>
+          <t>-10,5; 19,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 12,63</t>
+          <t>-30,12; -5,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,68%</t>
+          <t>-7,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,72</t>
+          <t>-4,37; 5,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -1,87</t>
+          <t>-12,17; -1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 7,08</t>
+          <t>-2,84; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,5</t>
+          <t>-5,02; 3,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 36,49</t>
+          <t>-21,25; 34,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -8,41</t>
+          <t>-48,06; -8,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 52,03</t>
+          <t>-15,03; 43,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 30,08</t>
+          <t>-29,09; 25,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>-21,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,66</t>
+          <t>-5,0; -1,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -2,46</t>
+          <t>-5,88; -2,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,7</t>
+          <t>-1,68; 1,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,1</t>
+          <t>-5,47; -1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,18; -11,33</t>
+          <t>-30,11; -11,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,38; -14,92</t>
+          <t>-31,7; -14,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 13,8</t>
+          <t>-11,93; 14,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 0,2</t>
+          <t>-29,87; -11,12</t>
         </is>
       </c>
     </row>
